--- a/apps_nicolo/LogicCircuits_4s_6r_HF_REINFORCE/LogicCircuits_5+3s_8r_HF_REINFORCE_SIL.xlsx
+++ b/apps_nicolo/LogicCircuits_4s_6r_HF_REINFORCE/LogicCircuits_5+3s_8r_HF_REINFORCE_SIL.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,13 +18,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +41,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -46,13 +58,37 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -131,10 +167,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -172,69 +208,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -258,54 +296,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -315,7 +352,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -324,7 +361,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -333,7 +370,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -341,10 +378,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -373,7 +410,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -386,13 +423,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -412,437 +448,550 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="178" customWidth="1" min="14" max="14"/>
-    <col width="76" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="35" customWidth="1" min="22" max="22"/>
-    <col width="80" customWidth="1" min="23" max="23"/>
-    <col width="135" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="99" customWidth="1" min="26" max="26"/>
+    <col width="21" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
+    <col width="14.14785714285714" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="18" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="7" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="10" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="10" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="17" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
+    <col width="10" bestFit="1" customWidth="1" style="8" min="10" max="10"/>
+    <col width="10" bestFit="1" customWidth="1" style="8" min="11" max="11"/>
+    <col width="17" bestFit="1" customWidth="1" style="8" min="12" max="12"/>
+    <col width="8" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
+    <col width="178" bestFit="1" customWidth="1" style="6" min="14" max="14"/>
+    <col width="76" bestFit="1" customWidth="1" style="6" min="15" max="15"/>
+    <col width="17" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
+    <col width="10" bestFit="1" customWidth="1" style="8" min="17" max="17"/>
+    <col width="17" bestFit="1" customWidth="1" style="8" min="18" max="18"/>
+    <col width="14" bestFit="1" customWidth="1" style="8" min="19" max="19"/>
+    <col width="22" bestFit="1" customWidth="1" style="8" min="20" max="20"/>
+    <col width="18" bestFit="1" customWidth="1" style="8" min="21" max="21"/>
+    <col width="35" bestFit="1" customWidth="1" style="6" min="22" max="22"/>
+    <col width="80" bestFit="1" customWidth="1" style="6" min="23" max="23"/>
+    <col width="135" bestFit="1" customWidth="1" style="6" min="24" max="24"/>
+    <col width="19" bestFit="1" customWidth="1" style="6" min="25" max="25"/>
+    <col width="99" bestFit="1" customWidth="1" style="6" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Epochs Completed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Saved</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Learning Rate</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Epochs #</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>(m, n, p, N)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>NN Depth</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>NN Width</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Deep Layer Size</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>CPUs #</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Entropy Scheduler</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Risk Scheduler</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Render Schedule</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>HoF Size</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Simulation Time</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Time Steps #</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="8" t="inlineStr">
         <is>
           <t>Initial Conditions #</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="8" t="inlineStr">
         <is>
           <t>Input Scenarios#</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>Continuous Distribution</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>Entropy Weights per Head</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>Structure Head Temperature</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>Ordering Enforced</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>SIL Settings</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2025-12-11 17:36:40</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>https://www.comet.com/redsnic/logiccircuits-5-3s-8r-hf-reinforce-sil/214a2855556843c28d5e012a0857369f</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="4" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>(8, 9, 5, 1280)</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="5" t="n">
         <v>1024</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="5" t="n">
         <v>10240</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="6" t="inlineStr">
         <is>
           <t>{'type': 'lognormal_independent'}</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="6" t="inlineStr">
         <is>
           <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="6" t="inlineStr">
         <is>
           <t>{'target_entropy_ratio_to_max': np.float64(0.22070261886581274), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="6" t="inlineStr">
         <is>
           <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2025-12-12 11:16:29</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>https://www.comet.com/redsnic/logiccircuits-5-3s-8r-hf-reinforce-sil/47371cdd309a401ca9bddbf7b8e43090</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="4" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>(8, 9, 5, 1280)</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="5" t="n">
         <v>1024</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="5" t="n">
         <v>10240</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>{'type': 'lognormal_independent'}</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>{'target_entropy_ratio_to_max': np.float64(0.22070261886581274), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z3" s="6" t="inlineStr">
         <is>
           <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2025-12-14 10:58:13</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>https://www.comet.com/redsnic/logiccircuits-5-3s-8r-hf-reinforce-sil/bf6d4ea5ec3e4499b352bbfb5a2f36f8</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="4" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>(8, 9, 5, 1280)</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="5" t="n">
         <v>1024</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="5" t="n">
         <v>10240</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>{'type': 'lognormal_independent'}</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="6" t="inlineStr">
         <is>
           <t>{'target_entropy_ratio_to_max': np.float64(0.17729310501000814), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-09 13:14:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/logiccircuits-5-3s-8r-hf-reinforce-sil/246ec6f4c2754f418dddacdbcb80d352</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>(8, 9, 5, 1280)</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M5" t="n">
+        <v>128</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>30</v>
+      </c>
+      <c r="R5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>32</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.22070261886581274), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Z5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>